--- a/2026A/心理学実験2/実験2_3_運動技能学習におけるフィードバック効果/実験3_フィードバック効果_18名の結果_260614.xlsx
+++ b/2026A/心理学実験2/実験2_3_運動技能学習におけるフィードバック効果/実験3_フィードバック効果_18名の結果_260614.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\matsu\github\OUJ\2026A\心理学実験2\実験2_3_運動技能学習におけるフィードバック効果\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86313687-2219-446D-961F-A7298C23F7F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBB96857-396B-4AF1-8696-15BB1CA3EFCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,9 +26,6 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -273,7 +270,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -310,16 +307,7 @@
     <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -641,6 +629,61 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="ja-JP" altLang="en-US"/>
+                  <a:t>ブロック</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="ja-JP"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -705,6 +748,66 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="ja-JP" altLang="en-US"/>
+                  <a:t>平均絶対誤差</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" altLang="ja-JP"/>
+                  <a:t>(cm)</a:t>
+                </a:r>
+                <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="ja-JP"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="0.00" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -781,6 +884,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -788,7 +892,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1421,9 +1524,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1461,9 +1564,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1496,26 +1599,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1548,26 +1634,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1742,32 +1811,32 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J23"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="24.6" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="24.65" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="7.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="13.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="10" width="13.33203125" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="7.36328125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="13.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="13.36328125" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.90625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="24.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" ht="24.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="3"/>
       <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-    </row>
-    <row r="2" spans="1:10" ht="24.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
+    </row>
+    <row r="2" spans="1:10" ht="24.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3"/>
       <c r="B2" s="3" t="s">
         <v>10</v>
@@ -1797,267 +1866,267 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:10" s="12" customFormat="1" ht="24.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="13">
+    <row r="3" spans="1:10" ht="24.65" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="12">
         <v>1</v>
       </c>
-      <c r="B3" s="14">
+      <c r="B3" s="12">
         <v>1</v>
       </c>
-      <c r="C3" s="15">
+      <c r="C3" s="11">
         <v>0.5</v>
       </c>
-      <c r="D3" s="15">
+      <c r="D3" s="11">
         <v>0.32</v>
       </c>
-      <c r="E3" s="15">
+      <c r="E3" s="11">
         <v>0.42</v>
       </c>
-      <c r="F3" s="15">
+      <c r="F3" s="11">
         <v>0.38</v>
       </c>
-      <c r="G3" s="15">
+      <c r="G3" s="11">
         <v>0.14000000000000001</v>
       </c>
-      <c r="H3" s="15">
+      <c r="H3" s="11">
         <v>0.14000000000000001</v>
       </c>
-      <c r="I3" s="15">
+      <c r="I3" s="11">
         <v>0.22</v>
       </c>
-      <c r="J3" s="15">
+      <c r="J3" s="11">
         <v>0.24</v>
       </c>
     </row>
-    <row r="4" spans="1:10" s="12" customFormat="1" ht="24.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="13">
+    <row r="4" spans="1:10" ht="24.65" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="12">
         <v>2</v>
       </c>
-      <c r="B4" s="14">
+      <c r="B4" s="12">
         <v>1</v>
       </c>
-      <c r="C4" s="15">
+      <c r="C4" s="11">
         <v>1.46</v>
       </c>
-      <c r="D4" s="15">
+      <c r="D4" s="11">
         <v>0.78</v>
       </c>
-      <c r="E4" s="15">
+      <c r="E4" s="11">
         <v>1.1200000000000001</v>
       </c>
-      <c r="F4" s="15">
+      <c r="F4" s="11">
         <v>0.3</v>
       </c>
-      <c r="G4" s="15">
+      <c r="G4" s="11">
         <v>0.46</v>
       </c>
-      <c r="H4" s="15">
+      <c r="H4" s="11">
         <v>0.28000000000000003</v>
       </c>
-      <c r="I4" s="15">
+      <c r="I4" s="11">
         <v>0.2</v>
       </c>
-      <c r="J4" s="15">
+      <c r="J4" s="11">
         <v>0.44</v>
       </c>
     </row>
-    <row r="5" spans="1:10" s="12" customFormat="1" ht="24.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="13">
+    <row r="5" spans="1:10" ht="24.65" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="12">
         <v>3</v>
       </c>
-      <c r="B5" s="14">
+      <c r="B5" s="12">
         <v>1</v>
       </c>
-      <c r="C5" s="15">
+      <c r="C5" s="11">
         <v>2.72</v>
       </c>
-      <c r="D5" s="15">
+      <c r="D5" s="11">
         <v>1.66</v>
       </c>
-      <c r="E5" s="15">
+      <c r="E5" s="11">
         <v>1.8</v>
       </c>
-      <c r="F5" s="15">
+      <c r="F5" s="11">
         <v>1.7</v>
       </c>
-      <c r="G5" s="15">
+      <c r="G5" s="11">
         <v>3.86</v>
       </c>
-      <c r="H5" s="15">
+      <c r="H5" s="11">
         <v>2.54</v>
       </c>
-      <c r="I5" s="15">
+      <c r="I5" s="11">
         <v>3.32</v>
       </c>
-      <c r="J5" s="15">
+      <c r="J5" s="11">
         <v>2.72</v>
       </c>
     </row>
-    <row r="6" spans="1:10" s="12" customFormat="1" ht="24.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="13">
+    <row r="6" spans="1:10" ht="24.65" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="12">
         <v>4</v>
       </c>
-      <c r="B6" s="14">
+      <c r="B6" s="12">
         <v>1</v>
       </c>
-      <c r="C6" s="15">
+      <c r="C6" s="11">
         <v>1.86</v>
       </c>
-      <c r="D6" s="15">
+      <c r="D6" s="11">
         <v>0.56000000000000005</v>
       </c>
-      <c r="E6" s="15">
+      <c r="E6" s="11">
         <v>0.42</v>
       </c>
-      <c r="F6" s="15">
+      <c r="F6" s="11">
         <v>0.52</v>
       </c>
-      <c r="G6" s="15">
+      <c r="G6" s="11">
         <v>2.12</v>
       </c>
-      <c r="H6" s="15">
+      <c r="H6" s="11">
         <v>2.54</v>
       </c>
-      <c r="I6" s="15">
+      <c r="I6" s="11">
         <v>2.62</v>
       </c>
-      <c r="J6" s="15">
+      <c r="J6" s="11">
         <v>2.2400000000000002</v>
       </c>
     </row>
-    <row r="7" spans="1:10" s="12" customFormat="1" ht="24.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="13">
+    <row r="7" spans="1:10" ht="24.65" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="12">
         <v>5</v>
       </c>
-      <c r="B7" s="14">
+      <c r="B7" s="12">
         <v>1</v>
       </c>
-      <c r="C7" s="15">
+      <c r="C7" s="11">
         <v>1.58</v>
       </c>
-      <c r="D7" s="15">
+      <c r="D7" s="11">
         <v>1.76</v>
       </c>
-      <c r="E7" s="15">
+      <c r="E7" s="11">
         <v>1.7</v>
       </c>
-      <c r="F7" s="15">
+      <c r="F7" s="11">
         <v>1.3</v>
       </c>
-      <c r="G7" s="15">
+      <c r="G7" s="11">
         <v>0.44</v>
       </c>
-      <c r="H7" s="15">
+      <c r="H7" s="11">
         <v>1</v>
       </c>
-      <c r="I7" s="15">
+      <c r="I7" s="11">
         <v>1.28</v>
       </c>
-      <c r="J7" s="15">
+      <c r="J7" s="11">
         <v>1.82</v>
       </c>
     </row>
-    <row r="8" spans="1:10" s="12" customFormat="1" ht="24.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="13">
+    <row r="8" spans="1:10" ht="24.65" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="12">
         <v>6</v>
       </c>
-      <c r="B8" s="14">
+      <c r="B8" s="12">
         <v>1</v>
       </c>
-      <c r="C8" s="15">
+      <c r="C8" s="11">
         <v>1.38</v>
       </c>
-      <c r="D8" s="15">
+      <c r="D8" s="11">
         <v>1.02</v>
       </c>
-      <c r="E8" s="15">
+      <c r="E8" s="11">
         <v>1.22</v>
       </c>
-      <c r="F8" s="15">
+      <c r="F8" s="11">
         <v>0.82</v>
       </c>
-      <c r="G8" s="15">
+      <c r="G8" s="11">
         <v>0.5</v>
       </c>
-      <c r="H8" s="15">
+      <c r="H8" s="11">
         <v>0.7</v>
       </c>
-      <c r="I8" s="15">
+      <c r="I8" s="11">
         <v>0.78</v>
       </c>
-      <c r="J8" s="15">
+      <c r="J8" s="11">
         <v>0.56000000000000005</v>
       </c>
     </row>
-    <row r="9" spans="1:10" s="12" customFormat="1" ht="24.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="13">
+    <row r="9" spans="1:10" ht="24.65" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="12">
         <v>7</v>
       </c>
-      <c r="B9" s="14">
+      <c r="B9" s="12">
         <v>1</v>
       </c>
-      <c r="C9" s="15">
+      <c r="C9" s="11">
         <v>7.9</v>
       </c>
-      <c r="D9" s="15">
+      <c r="D9" s="11">
         <v>6.8</v>
       </c>
-      <c r="E9" s="15">
+      <c r="E9" s="11">
         <v>7.1</v>
       </c>
-      <c r="F9" s="15">
+      <c r="F9" s="11">
         <v>7.3</v>
       </c>
-      <c r="G9" s="15">
+      <c r="G9" s="11">
         <v>7.4</v>
       </c>
-      <c r="H9" s="15">
+      <c r="H9" s="11">
         <v>6.6</v>
       </c>
-      <c r="I9" s="15">
+      <c r="I9" s="11">
         <v>7.3</v>
       </c>
-      <c r="J9" s="15">
+      <c r="J9" s="11">
         <v>6.6</v>
       </c>
     </row>
-    <row r="10" spans="1:10" s="12" customFormat="1" ht="24.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="13">
+    <row r="10" spans="1:10" ht="24.65" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="12">
         <v>8</v>
       </c>
-      <c r="B10" s="14">
+      <c r="B10" s="12">
         <v>2</v>
       </c>
-      <c r="C10" s="15">
+      <c r="C10" s="11">
         <v>1.96</v>
       </c>
-      <c r="D10" s="15">
+      <c r="D10" s="11">
         <v>2.2000000000000002</v>
       </c>
-      <c r="E10" s="15">
+      <c r="E10" s="11">
         <v>1.22</v>
       </c>
-      <c r="F10" s="15">
+      <c r="F10" s="11">
         <v>0.24</v>
       </c>
-      <c r="G10" s="15">
+      <c r="G10" s="11">
         <v>0.5</v>
       </c>
-      <c r="H10" s="15">
+      <c r="H10" s="11">
         <v>0.48</v>
       </c>
-      <c r="I10" s="15">
+      <c r="I10" s="11">
         <v>0.46</v>
       </c>
-      <c r="J10" s="15">
+      <c r="J10" s="11">
         <v>0.56000000000000005</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="24.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="13">
+    <row r="11" spans="1:10" ht="24.65" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="12">
         <v>9</v>
       </c>
-      <c r="B11" s="14">
+      <c r="B11" s="12">
         <v>2</v>
       </c>
       <c r="C11" s="11">
@@ -2085,11 +2154,11 @@
         <v>2.74</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="24.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="13">
+    <row r="12" spans="1:10" ht="24.65" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="12">
         <v>10</v>
       </c>
-      <c r="B12" s="14">
+      <c r="B12" s="12">
         <v>2</v>
       </c>
       <c r="C12" s="11">
@@ -2117,11 +2186,11 @@
         <v>12.24</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="24.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="13">
+    <row r="13" spans="1:10" ht="24.65" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="12">
         <v>11</v>
       </c>
-      <c r="B13" s="14">
+      <c r="B13" s="12">
         <v>2</v>
       </c>
       <c r="C13" s="11">
@@ -2149,11 +2218,11 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="24.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="13">
+    <row r="14" spans="1:10" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="12">
         <v>12</v>
       </c>
-      <c r="B14" s="14">
+      <c r="B14" s="12">
         <v>2</v>
       </c>
       <c r="C14" s="11">
@@ -2181,11 +2250,11 @@
         <v>3.24</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="24.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="13">
+    <row r="15" spans="1:10" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="12">
         <v>13</v>
       </c>
-      <c r="B15" s="13">
+      <c r="B15" s="12">
         <v>3</v>
       </c>
       <c r="C15" s="11">
@@ -2213,11 +2282,11 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="24.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="13">
+    <row r="16" spans="1:10" ht="24.65" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="12">
         <v>14</v>
       </c>
-      <c r="B16" s="13">
+      <c r="B16" s="12">
         <v>3</v>
       </c>
       <c r="C16" s="11">
@@ -2245,11 +2314,11 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="24.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="13">
+    <row r="17" spans="1:10" ht="24.65" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="12">
         <v>15</v>
       </c>
-      <c r="B17" s="13">
+      <c r="B17" s="12">
         <v>3</v>
       </c>
       <c r="C17" s="11">
@@ -2277,11 +2346,11 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="24.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="13">
+    <row r="18" spans="1:10" ht="24.65" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="12">
         <v>16</v>
       </c>
-      <c r="B18" s="13">
+      <c r="B18" s="12">
         <v>3</v>
       </c>
       <c r="C18" s="11">
@@ -2309,11 +2378,11 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="24.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="13">
+    <row r="19" spans="1:10" ht="24.65" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="12">
         <v>17</v>
       </c>
-      <c r="B19" s="13">
+      <c r="B19" s="12">
         <v>3</v>
       </c>
       <c r="C19" s="11">
@@ -2341,11 +2410,11 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="24.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="13">
+    <row r="20" spans="1:10" ht="24.65" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="12">
         <v>18</v>
       </c>
-      <c r="B20" s="13">
+      <c r="B20" s="12">
         <v>3</v>
       </c>
       <c r="C20" s="11">
@@ -2373,7 +2442,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="24.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10" ht="24.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B21" s="1">
         <v>1</v>
       </c>
@@ -2410,7 +2479,7 @@
         <v>2.0885714285714285</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="24.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10" ht="24.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B22" s="1">
         <v>2</v>
       </c>
@@ -2447,7 +2516,7 @@
         <v>3.8240000000000003</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="24.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10" ht="24.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B23" s="1">
         <v>3</v>
       </c>
@@ -2500,13 +2569,13 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.649999999999999" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="4"/>
-    <col min="2" max="2" width="12.77734375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="12.44140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="10" width="10.21875" style="4" customWidth="1"/>
+    <col min="2" max="2" width="12.81640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="12.453125" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="10.1796875" style="4" customWidth="1"/>
     <col min="11" max="11" width="9" style="4"/>
-    <col min="12" max="12" width="12.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.21875" style="7" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.90625" style="4" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.1796875" style="7" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.08984375" style="7" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="9" style="7"/>
     <col min="16" max="16384" width="9" style="4"/>
   </cols>
